--- a/a/links_cfe.xlsx
+++ b/a/links_cfe.xlsx
@@ -913,7 +913,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">

--- a/a/links_cfe.xlsx
+++ b/a/links_cfe.xlsx
@@ -467,7 +467,11 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/startup-huddle-source.txt</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Startup Huddle</t>
@@ -513,7 +517,11 @@
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/g20-young-entrepreneurs-alliance-source.txt</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>G20 Young Entrepreneurs Alliance</t>
@@ -531,8 +539,16 @@
           <t>/programs/dynamic-entrepreneurship-classroom</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/dynamic-entrepreneurship-classroom-source.txt</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Dynamic Entrepreneurship Classroom</t>
@@ -551,7 +567,11 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/scaleup-acceleration-program-source.txt</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Scaleup Acceleration Program</t>
@@ -570,7 +590,11 @@
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/scaleup-club-source.txt</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Scaleup Club</t>
@@ -589,7 +613,11 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/startup-club-source.txt</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Startup Club</t>
@@ -608,7 +636,11 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/fasttrac-source.txt</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Fasttrac</t>
@@ -627,7 +659,11 @@
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/acceleration-programs-source.txt</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Acceleration Programs</t>
@@ -646,7 +682,11 @@
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/startup-programs-source.txt</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Startup Programs</t>
@@ -665,7 +705,11 @@
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/educational-programs-source.txt</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Educational Programs</t>
@@ -684,7 +728,11 @@
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/ecosystem-programs-source.txt</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Ecosystem Programs</t>
@@ -703,7 +751,11 @@
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/launch-startup-source.txt</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Launch Startup</t>
@@ -722,7 +774,11 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/grow-existing-business-source.txt</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Grow Existing Business</t>
@@ -741,7 +797,11 @@
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/support-entrepreneurship-source.txt</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>Support Entrepreneurship</t>
@@ -760,7 +820,11 @@
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/launch-startup-source.txt</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Launch Startup</t>
@@ -779,7 +843,11 @@
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/mentoring-business-source.txt</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Mentoring Business</t>
@@ -798,7 +866,11 @@
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/mentoring-programs-source.txt</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Mentoring Programs</t>
@@ -817,7 +889,11 @@
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/scale-up-programs-source.txt</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>Scale Up Programs</t>
@@ -836,7 +912,11 @@
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/best-practices-source.txt</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Best Practices</t>
@@ -855,7 +935,11 @@
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/learn-entrepreneurship-source.txt</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Learn Entrepreneurship</t>
@@ -874,7 +958,11 @@
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/partners/global-entrepreneurship-network-source.txt</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Global Entrepreneurship Network</t>
@@ -893,7 +981,11 @@
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/partners/ewing-marion-kauffman-foundation-source.txt</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Ewing Marion Kauffman Foundation</t>

--- a/a/links_cfe.xlsx
+++ b/a/links_cfe.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/a/links_cfe.xlsx
+++ b/a/links_cfe.xlsx
@@ -986,7 +986,11 @@
           <t>/partners/ewing-marion-kauffman-foundation</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>https://cfeglobal.org/partners/ewing-marion-kauffman-foundation-source.txt</t>
@@ -1072,7 +1076,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">

--- a/a/links_cfe.xlsx
+++ b/a/links_cfe.xlsx
@@ -988,7 +988,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">

--- a/a/links_cfe.xlsx
+++ b/a/links_cfe.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="82">
   <si>
     <t>topic</t>
   </si>
@@ -248,6 +249,18 @@
   </si>
   <si>
     <t>https://dochub.sk.ru/foundation/itc/b/news/archive/2020/12/18/kompanii-skolkovo-rasskazali-o-svoih-resheniyah-v-oblasti-ai-na-startup-klube-delovoy-rossii.aspx</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>/partners/young-entrepreneurs-organization</t>
+  </si>
+  <si>
+    <t>/partners/american-chamber-of-commerce</t>
+  </si>
+  <si>
+    <t>/partners/junior-achievement</t>
   </si>
 </sst>
 </file>
@@ -607,8 +620,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="34.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -945,6 +961,9 @@
       <c r="B21" t="s">
         <v>65</v>
       </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
       <c r="D21" t="s">
         <v>66</v>
       </c>
@@ -1019,7 +1038,62 @@
         <v>77</v>
       </c>
     </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" t="str">
+        <f>CONCATENATE("https://cfeglobal.org",B27,".txt")</f>
+        <v>https://cfeglobal.org/partners/young-entrepreneurs-organization.txt</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" ref="D28:D29" si="0">CONCATENATE("https://cfeglobal.org",B28,".txt")</f>
+        <v>https://cfeglobal.org/partners/american-chamber-of-commerce.txt</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="0"/>
+        <v>https://cfeglobal.org/partners/junior-achievement.txt</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/a/links_cfe.xlsx
+++ b/a/links_cfe.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,10 +840,14 @@
           <t>/programs/mentoring-programs</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://cfeglobal.org/programs/mentoring-programs-source.txt</t>
+          <t>https://cfeglobal.org/programs/mentoring-programs.txt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -866,7 +870,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://cfeglobal.org/programs/scale-up-programs-source.txt</t>
+          <t>https://cfeglobal.org/programs/scale-up-programs.txt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -886,10 +890,14 @@
           <t>/programs/best-practices</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://cfeglobal.org/programs/best-practices-source.txt</t>
+          <t>https://cfeglobal.org/programs/best-practices.txt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -965,7 +973,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1103,7 +1111,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1130,7 +1138,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1157,17 +1165,44 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/partners/junior-achievement.txt</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Junior Achievement</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>programs</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>/programs/dedicated-team</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://cfeglobal.org/partners/junior-achievement.txt</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Junior Achievement</t>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://cfeglobal.org/programs/dedicated-team.txt</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Dedicated Team</t>
         </is>
       </c>
     </row>
